--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9598,8 +9598,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -9623,6 +9623,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -9697,6 +9699,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -9849,10 +9861,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E7086F0-770B-4323-8BF9-02EC28EAB4FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC323E73-6D4D-472E-9769-DA43278CADDA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958A80CB-35A6-4507-9FC9-D9DC95A13CE9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A3E0F40-1F97-4B03-BCFA-8E42EFA81125}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9598,8 +9598,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -9623,6 +9623,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -9697,6 +9699,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -9850,7 +9862,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E7086F0-770B-4323-8BF9-02EC28EAB4FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2CD72C2-B736-4967-8C85-91B91269CC3D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9598,8 +9598,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -9623,6 +9623,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -9697,6 +9699,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -9849,10 +9861,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E7086F0-770B-4323-8BF9-02EC28EAB4FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B05BEBDD-CFD3-4B2A-9852-A0B7B463A3B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958A80CB-35A6-4507-9FC9-D9DC95A13CE9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{714B397A-BC0F-4976-BBA6-858E1157EA56}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9861,10 +9861,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2CD72C2-B736-4967-8C85-91B91269CC3D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958A80CB-35A6-4507-9FC9-D9DC95A13CE9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F32684B-38D1-4211-815E-2266952D98F4}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9861,10 +9861,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2CD72C2-B736-4967-8C85-91B91269CC3D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958A80CB-35A6-4507-9FC9-D9DC95A13CE9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACBC29A0-6F58-4568-94F3-33E406DCADFF}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9861,10 +9861,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2CD72C2-B736-4967-8C85-91B91269CC3D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958A80CB-35A6-4507-9FC9-D9DC95A13CE9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95487CC6-6B81-4269-B09D-FE1477DE21E1}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F5CF888-7AE0-4234-A808-9AC88891EDB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8E5355C-3D90-4973-A97A-767428282CF4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB50B76B-67F3-42FF-81F7-3BDB0E6A0441}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1D0A277-A532-4B2E-A1D1-3D94DC09DA61}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54F2A531-2CDC-4E7F-A058-32AF2FA3961C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{351B5A43-2ED8-40E6-ABA6-8364C9D71228}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -762,7 +762,7 @@
         <v>2.99</v>
       </c>
       <c r="K4">
-        <v>90.94583333</v>
+        <v>90.94583333000001</v>
       </c>
       <c r="L4">
         <v>90</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.0999999999999996</t>
         </is>
       </c>
       <c r="AD6">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>9.300000000000001</t>
+          <t>9.3000000000000007</t>
         </is>
       </c>
       <c r="AD18">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>8.550000000000001</t>
+          <t>8.5500000000000007</t>
         </is>
       </c>
       <c r="AF31">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>36.090000000000003</t>
         </is>
       </c>
       <c r="AD35">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>8.699999999999999</t>
+          <t>8.6999999999999993</t>
         </is>
       </c>
       <c r="AD80">
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8E5355C-3D90-4973-A97A-767428282CF4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EF1CB4B-6FEE-4F62-A99D-389E77B445ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1D0A277-A532-4B2E-A1D1-3D94DC09DA61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1918AB84-B61F-49CA-BBFD-8F9BAE64F280}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{351B5A43-2ED8-40E6-ABA6-8364C9D71228}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12CC5DCE-7F99-41C0-9E10-605F09E2375B}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EF1CB4B-6FEE-4F62-A99D-389E77B445ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04040E3C-1A96-42C2-BB0C-249D6ED71FAE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1918AB84-B61F-49CA-BBFD-8F9BAE64F280}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7717E6EB-4012-40CD-A21F-FC663DA600BE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12CC5DCE-7F99-41C0-9E10-605F09E2375B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{962B3103-A659-497D-B4C7-229E8FC4B1A8}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -762,7 +762,7 @@
         <v>2.99</v>
       </c>
       <c r="K4">
-        <v>90.94583333</v>
+        <v>90.94583333000001</v>
       </c>
       <c r="L4">
         <v>90</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.0999999999999996</t>
         </is>
       </c>
       <c r="AD6">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>9.300000000000001</t>
+          <t>9.3000000000000007</t>
         </is>
       </c>
       <c r="AD18">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>8.550000000000001</t>
+          <t>8.5500000000000007</t>
         </is>
       </c>
       <c r="AF31">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>36.090000000000003</t>
         </is>
       </c>
       <c r="AD35">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>8.699999999999999</t>
+          <t>8.6999999999999993</t>
         </is>
       </c>
       <c r="AD80">
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8E5355C-3D90-4973-A97A-767428282CF4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECC16C6F-578F-4421-B0B7-96E5A3983F07}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1D0A277-A532-4B2E-A1D1-3D94DC09DA61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6EE0C3-7055-44DF-A84A-BEEAFA94924D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{351B5A43-2ED8-40E6-ABA6-8364C9D71228}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{947BB220-8503-4BE9-ABF5-9CF05A86535F}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04040E3C-1A96-42C2-BB0C-249D6ED71FAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42EB3E17-65E4-4AA4-81BA-82BD6A5239D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7717E6EB-4012-40CD-A21F-FC663DA600BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{726BE847-9D23-4C92-A8FA-B7CA92B4C3F4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{962B3103-A659-497D-B4C7-229E8FC4B1A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEF527B-9B2B-4F36-BB8A-E0470EFA60CC}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42EB3E17-65E4-4AA4-81BA-82BD6A5239D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E31742-9916-4317-956D-EBB8067B64A6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{726BE847-9D23-4C92-A8FA-B7CA92B4C3F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C7E57AF-D593-4683-9E8B-DB13022E9665}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEF527B-9B2B-4F36-BB8A-E0470EFA60CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BE6C75-7FF8-4375-8C37-700ECFDDFCA6}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E31742-9916-4317-956D-EBB8067B64A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FBB6A88-28FE-4177-ADB2-1D4451380366}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C7E57AF-D593-4683-9E8B-DB13022E9665}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E19B1302-8750-496C-A790-A43823A8CD90}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BE6C75-7FF8-4375-8C37-700ECFDDFCA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D750933-FFBF-41EF-AF27-1B417293EAA6}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FBB6A88-28FE-4177-ADB2-1D4451380366}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36130B4F-06A9-4A44-8C30-3539A188B3E3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E19B1302-8750-496C-A790-A43823A8CD90}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5098C73B-C567-447C-BF9B-DC079F4DA29D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D750933-FFBF-41EF-AF27-1B417293EAA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BEBD78-6A46-4020-9612-7EBB163B8129}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36130B4F-06A9-4A44-8C30-3539A188B3E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57972058-47E6-4299-8400-80A5A2078F18}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5098C73B-C567-447C-BF9B-DC079F4DA29D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E07D456C-7E41-4127-B480-EFEB13E7FC52}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BEBD78-6A46-4020-9612-7EBB163B8129}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4D9428-1DE5-4C85-B1B4-1476800A2BC5}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57972058-47E6-4299-8400-80A5A2078F18}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D806C5-4668-42B9-8E05-8A7278AD837D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E07D456C-7E41-4127-B480-EFEB13E7FC52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E6B0266-CD6C-4CFF-AA4B-90E8886E871F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4D9428-1DE5-4C85-B1B4-1476800A2BC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AD896CD-5361-4A5A-B9DE-10F87D8647D3}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D806C5-4668-42B9-8E05-8A7278AD837D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAA8ABAF-F49F-4BCB-8F28-92A543AFF395}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E6B0266-CD6C-4CFF-AA4B-90E8886E871F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FF4D488-1ECE-4898-935B-E278A3672648}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AD896CD-5361-4A5A-B9DE-10F87D8647D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDC52BD-C2EF-44CC-939B-B32CB493FEDF}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAA8ABAF-F49F-4BCB-8F28-92A543AFF395}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D94498D-7245-4B30-BC2F-3561487C6D2D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FF4D488-1ECE-4898-935B-E278A3672648}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17E50640-390B-4882-9048-EFDA7475992E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDC52BD-C2EF-44CC-939B-B32CB493FEDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BEEC9A9-8DD2-49DE-9372-30BC5C66B960}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D94498D-7245-4B30-BC2F-3561487C6D2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC958ECC-8CA0-41BD-BDAC-FF1C63E6109F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17E50640-390B-4882-9048-EFDA7475992E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45B33E89-64E1-4698-9B21-2D08713D5286}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BEEC9A9-8DD2-49DE-9372-30BC5C66B960}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73CF2D6-836B-44A7-80AB-A03DB5CDA185}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC958ECC-8CA0-41BD-BDAC-FF1C63E6109F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8C7F7F1-4763-4285-B21C-ECF40CF7A9A3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45B33E89-64E1-4698-9B21-2D08713D5286}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B124948-D275-47BE-8749-13F231BD5221}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73CF2D6-836B-44A7-80AB-A03DB5CDA185}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56F39016-DBF4-4D68-A303-9896EEB9245D}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8C7F7F1-4763-4285-B21C-ECF40CF7A9A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E9FCB4B-9ED5-4D1D-8DB1-C9CE7E0725C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B124948-D275-47BE-8749-13F231BD5221}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A9FE1AC-D57B-4E4B-B5EA-C734F40056B1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56F39016-DBF4-4D68-A303-9896EEB9245D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55337D5F-10C7-453E-B23D-250B9E7C2F8F}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E9FCB4B-9ED5-4D1D-8DB1-C9CE7E0725C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E91699-B225-4992-BD23-66ACDCFDB9D7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A9FE1AC-D57B-4E4B-B5EA-C734F40056B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4419FE5D-A3A1-4120-AA22-F05D49E9F979}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55337D5F-10C7-453E-B23D-250B9E7C2F8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7813A063-D6CA-4E0D-AAAE-1950D72646D6}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E91699-B225-4992-BD23-66ACDCFDB9D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FED6FA7-661D-47F7-AE04-5B7353257235}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4419FE5D-A3A1-4120-AA22-F05D49E9F979}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{876D86F6-8CA1-4FE4-9D4D-51F393098CE0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7813A063-D6CA-4E0D-AAAE-1950D72646D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51C1CAB8-E598-4499-B15D-720A3CA8061B}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FED6FA7-661D-47F7-AE04-5B7353257235}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71B394AE-88D9-4A7C-B700-8F11B905DF92}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{876D86F6-8CA1-4FE4-9D4D-51F393098CE0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA613EC-A6ED-42FC-9A97-B33ECC68C28D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51C1CAB8-E598-4499-B15D-720A3CA8061B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3198BC3-9562-4D80-80FB-5C51B09B9904}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71B394AE-88D9-4A7C-B700-8F11B905DF92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2283A8CF-AC82-4A53-A9E2-35F48D59DCBF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA613EC-A6ED-42FC-9A97-B33ECC68C28D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{697A4A6C-B575-4DD0-B49E-DD7FF3F3F412}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3198BC3-9562-4D80-80FB-5C51B09B9904}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E485B4-D900-425C-A2B9-5C6906539280}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2283A8CF-AC82-4A53-A9E2-35F48D59DCBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83C1418E-536D-4A81-805C-07C79D8C2F26}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{697A4A6C-B575-4DD0-B49E-DD7FF3F3F412}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABB05EC6-D9B9-4629-A73F-C95EB9CC6C7B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E485B4-D900-425C-A2B9-5C6906539280}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{241B6E88-F3A6-4AC8-97D2-30C0D5EF45D2}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83C1418E-536D-4A81-805C-07C79D8C2F26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AD94DEF-B109-4EF0-84CF-46AC673918A8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABB05EC6-D9B9-4629-A73F-C95EB9CC6C7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022F96E8-F3CA-4976-BCC0-83DDE8530F61}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{241B6E88-F3A6-4AC8-97D2-30C0D5EF45D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF1ED3C9-3117-4886-8828-ABB462F82445}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AD94DEF-B109-4EF0-84CF-46AC673918A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D048D8-CFFA-48EF-9183-71CCDCB9830B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022F96E8-F3CA-4976-BCC0-83DDE8530F61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67659E34-047D-4EB6-844E-91F48C1A44C2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF1ED3C9-3117-4886-8828-ABB462F82445}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED30160D-CCA5-4C39-A81D-329E244D59D4}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D048D8-CFFA-48EF-9183-71CCDCB9830B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72319D58-21D7-4413-9CF5-EF34CC0945AB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67659E34-047D-4EB6-844E-91F48C1A44C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D010226-8D8F-451B-B8BE-61C5862F24D7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED30160D-CCA5-4C39-A81D-329E244D59D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0ED3DD6-C830-4EE7-99F0-8346D0F6195D}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72319D58-21D7-4413-9CF5-EF34CC0945AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D5154F1-CBA3-43CC-94C2-296D05052756}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D010226-8D8F-451B-B8BE-61C5862F24D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE6EFC03-B7EB-455F-BA13-564187AE0960}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0ED3DD6-C830-4EE7-99F0-8346D0F6195D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46F6AF2C-771F-4AE7-90DA-E3BBE6695956}"/>
 </file>